--- a/cds/mm_france-5year-cds.xlsx
+++ b/cds/mm_france-5year-cds.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="599">
   <si>
     <t>Date</t>
   </si>
@@ -1797,6 +1797,21 @@
   </si>
   <si>
     <t>2026-03-06</t>
+  </si>
+  <si>
+    <t>2026-03-13</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
   </si>
 </sst>
 </file>
@@ -2146,7 +2161,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B593"/>
+  <dimension ref="A1:B598"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -6891,6 +6906,46 @@
       </c>
       <c r="B593" s="3">
         <v>26.8451</v>
+      </c>
+    </row>
+    <row r="594" spans="1:2">
+      <c r="A594" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="B594" s="3">
+        <v>30.0233</v>
+      </c>
+    </row>
+    <row r="595" spans="1:2">
+      <c r="A595" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="B595" s="3">
+        <v>29.9326</v>
+      </c>
+    </row>
+    <row r="596" spans="1:2">
+      <c r="A596" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="B596" s="3">
+        <v>37.4156</v>
+      </c>
+    </row>
+    <row r="597" spans="1:2">
+      <c r="A597" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="B597" s="3">
+        <v>34.8148</v>
+      </c>
+    </row>
+    <row r="598" spans="1:2">
+      <c r="A598" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="B598" s="3">
+        <v>31.5878</v>
       </c>
     </row>
   </sheetData>
